--- a/_build/_merged/Original Sales May, June, July.xlsx
+++ b/_build/_merged/Original Sales May, June, July.xlsx
@@ -30486,6 +30486,9 @@
       <c r="Q246" s="2">
         <v>46247.77083333334</v>
       </c>
+      <c r="Y246">
+        <v>12980</v>
+      </c>
       <c r="AA246" t="s">
         <v>1224</v>
       </c>
@@ -30512,6 +30515,9 @@
       <c r="T247" t="s">
         <v>1183</v>
       </c>
+      <c r="Y247">
+        <v>65796</v>
+      </c>
       <c r="AA247" t="s">
         <v>1218</v>
       </c>
@@ -30538,6 +30544,9 @@
       <c r="T248" t="s">
         <v>1184</v>
       </c>
+      <c r="Y248">
+        <v>38940</v>
+      </c>
       <c r="AA248" t="s">
         <v>1216</v>
       </c>
@@ -30561,6 +30570,9 @@
       <c r="Q249" s="2">
         <v>46247.92291666667</v>
       </c>
+      <c r="Y249">
+        <v>62000</v>
+      </c>
       <c r="AA249" t="s">
         <v>1218</v>
       </c>
@@ -30587,6 +30599,9 @@
       <c r="T250" t="s">
         <v>1185</v>
       </c>
+      <c r="Y250">
+        <v>26000</v>
+      </c>
       <c r="AA250" t="s">
         <v>1222</v>
       </c>
@@ -30613,6 +30628,9 @@
       <c r="T251" t="s">
         <v>1186</v>
       </c>
+      <c r="Y251">
+        <v>116192</v>
+      </c>
       <c r="AA251" t="s">
         <v>1221</v>
       </c>
@@ -30639,6 +30657,9 @@
       <c r="T252" t="s">
         <v>1187</v>
       </c>
+      <c r="Y252">
+        <v>54516</v>
+      </c>
       <c r="AA252" t="s">
         <v>1217</v>
       </c>
@@ -30665,6 +30686,9 @@
       <c r="T253" t="s">
         <v>1188</v>
       </c>
+      <c r="Y253">
+        <v>64900</v>
+      </c>
       <c r="AA253" t="s">
         <v>1218</v>
       </c>
@@ -30691,6 +30715,9 @@
       <c r="T254" t="s">
         <v>1189</v>
       </c>
+      <c r="Y254">
+        <v>68000</v>
+      </c>
       <c r="AA254" t="s">
         <v>1222</v>
       </c>
@@ -30717,6 +30744,9 @@
       <c r="T255" t="s">
         <v>1188</v>
       </c>
+      <c r="Y255">
+        <v>54516</v>
+      </c>
       <c r="AA255" t="s">
         <v>1218</v>
       </c>
@@ -30743,6 +30773,9 @@
       <c r="T256" t="s">
         <v>1190</v>
       </c>
+      <c r="Y256">
+        <v>63000</v>
+      </c>
       <c r="AA256" t="s">
         <v>1234</v>
       </c>
@@ -30769,6 +30802,9 @@
       <c r="T257" t="s">
         <v>1191</v>
       </c>
+      <c r="Y257">
+        <v>12980</v>
+      </c>
       <c r="AA257" t="s">
         <v>1219</v>
       </c>
@@ -30795,6 +30831,9 @@
       <c r="T258" t="s">
         <v>1191</v>
       </c>
+      <c r="Y258">
+        <v>12980</v>
+      </c>
       <c r="AA258" t="s">
         <v>1228</v>
       </c>
@@ -30821,6 +30860,9 @@
       <c r="T259" t="s">
         <v>1188</v>
       </c>
+      <c r="Y259">
+        <v>54516</v>
+      </c>
       <c r="AA259" t="s">
         <v>1217</v>
       </c>
@@ -30847,6 +30889,9 @@
       <c r="T260" t="s">
         <v>1183</v>
       </c>
+      <c r="Y260">
+        <v>65768</v>
+      </c>
       <c r="AA260" t="s">
         <v>1216</v>
       </c>
@@ -30869,6 +30914,9 @@
       </c>
       <c r="Q261" s="2">
         <v>46250.94097222222</v>
+      </c>
+      <c r="Y261">
+        <v>83544</v>
       </c>
       <c r="AA261" t="s">
         <v>1218</v>
